--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Equity Minimum Variance Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Equity Minimum Variance Fund.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC7E6F8-9873-4F61-8907-98BC55C138B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303691CC-D0DC-4C61-AAF6-B24390FD408C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="134">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Equity Minimum Variance Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -67,28 +67,103 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
     <t>HDFC Bank Ltd.</t>
   </si>
   <si>
     <t>INE040A01034</t>
   </si>
   <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Tata Consultancy Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE467B01029</t>
-  </si>
-  <si>
-    <t>It - Software</t>
+    <t>Maruti Suzuki India Ltd.</t>
+  </si>
+  <si>
+    <t>INE585B01010</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Infosys Ltd.</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
   </si>
   <si>
     <t>State Bank Of India</t>
@@ -97,52 +172,73 @@
     <t>INE062A01020</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Infosys Ltd.</t>
-  </si>
-  <si>
-    <t>INE009A01021</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
+  </si>
+  <si>
+    <t>Power Grid Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE752E01010</t>
+  </si>
+  <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
   </si>
   <si>
     <t>Hindustan Unilever Ltd.</t>
@@ -151,52 +247,19 @@
     <t>INE030A01027</t>
   </si>
   <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Power Grid Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE752E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Cipla Ltd.</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
+  </si>
+  <si>
+    <t>Trent Ltd.</t>
+  </si>
+  <si>
+    <t>INE849A01020</t>
+  </si>
+  <si>
+    <t>Retailing</t>
   </si>
   <si>
     <t>Wipro Ltd.</t>
@@ -205,43 +268,10 @@
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Maruti Suzuki India Ltd.</t>
-  </si>
-  <si>
-    <t>INE585B01010</t>
+    <t>Tech Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE669C01036</t>
   </si>
   <si>
     <t>Britannia Industries Ltd.</t>
@@ -253,13 +283,10 @@
     <t>Food Products</t>
   </si>
   <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
+    <t>Nestle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE239A01024</t>
   </si>
   <si>
     <t>Titan Company Ltd.</t>
@@ -268,31 +295,13 @@
     <t>INE280A01028</t>
   </si>
   <si>
-    <t>Nestle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE239A01024</t>
-  </si>
-  <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Tech Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE669C01036</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>^</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd. (Covered call) $$</t>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>Oil</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -331,22 +340,19 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X383</t>
+    <t>IN002025X026</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>IN002024X417</t>
+    <t>IN002025X018</t>
   </si>
   <si>
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024Z040</t>
+    <t>IN002024Z164</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -385,16 +391,7 @@
     <t>ICICI Bank Ltd. $$</t>
   </si>
   <si>
-    <t>Sun Pharmaceutical Industries Ltd. $$</t>
-  </si>
-  <si>
-    <t>Nestle India Ltd. $$</t>
-  </si>
-  <si>
-    <t>Wipro Ltd. $$</t>
-  </si>
-  <si>
-    <t>Infosys Ltd. $$</t>
+    <t>Life Insurance Corporation Of India. $$</t>
   </si>
   <si>
     <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
@@ -406,16 +403,13 @@
     <t>$$ - Derivatives.</t>
   </si>
   <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -434,15 +428,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="##0.00"/>
     <numFmt numFmtId="165" formatCode="##0.00%"/>
-    <numFmt numFmtId="166" formatCode="\^"/>
-    <numFmt numFmtId="167" formatCode="##0"/>
+    <numFmt numFmtId="166" formatCode="##0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -629,7 +622,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
@@ -643,14 +636,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -680,7 +673,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -689,15 +682,12 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -730,13 +720,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -760,7 +750,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="20650200"/>
+          <a:off x="666750" y="19697700"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -777,13 +767,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -807,7 +797,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="23507700"/>
+          <a:off x="666750" y="22555200"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1143,19 +1133,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="25" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="53.85546875" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.85546875" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="47.140625" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="11" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="38.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="11.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="26.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="10" style="24" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="53.85546875" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.85546875" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.7109375" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="47.140625" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="10.85546875" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="38.7109375" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="11.7109375" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.7109375" style="24" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="26.7109375" style="24" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1243,10 +1233,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="12">
-        <v>288667.15000000002</v>
+        <v>315467.02999999997</v>
       </c>
       <c r="H5" s="13">
-        <v>0.85724252499530007</v>
+        <v>0.86516639338459989</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>13</v>
@@ -1280,10 +1270,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="12">
-        <v>288667.15000000002</v>
+        <v>315467.02999999997</v>
       </c>
       <c r="H7" s="13">
-        <v>0.85724252499530007</v>
+        <v>0.86516639338459989</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>13</v>
@@ -1306,13 +1296,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <v>1595381</v>
+        <v>1759560</v>
       </c>
       <c r="G8" s="18">
-        <v>27101.53</v>
+        <v>25001.59</v>
       </c>
       <c r="H8" s="19">
-        <v>8.0482257882299998E-2</v>
+        <v>6.8566707111099995E-2</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -1332,16 +1322,16 @@
         <v>13</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F9" s="17">
-        <v>1995596</v>
+        <v>1435596</v>
       </c>
       <c r="G9" s="18">
-        <v>25000.83</v>
+        <v>20755.849999999999</v>
       </c>
       <c r="H9" s="19">
-        <v>7.4243898677799999E-2</v>
+        <v>5.6922791222099998E-2</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>13</v>
@@ -1352,25 +1342,25 @@
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" s="17">
-        <v>390466</v>
+        <v>537485</v>
       </c>
       <c r="G10" s="18">
-        <v>16057.52</v>
+        <v>18615.259999999998</v>
       </c>
       <c r="H10" s="19">
-        <v>4.7685332362800002E-2</v>
+        <v>5.1052236286400002E-2</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>13</v>
@@ -1381,25 +1371,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F11" s="17">
-        <v>1995558</v>
+        <v>4402283</v>
       </c>
       <c r="G11" s="18">
-        <v>15423.67</v>
+        <v>18403.740000000002</v>
       </c>
       <c r="H11" s="19">
-        <v>4.5803015048600002E-2</v>
+        <v>5.0472143984800003E-2</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>13</v>
@@ -1410,25 +1400,25 @@
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F12" s="17">
-        <v>1558158</v>
+        <v>923629</v>
       </c>
       <c r="G12" s="18">
-        <v>15365</v>
+        <v>17963.66</v>
       </c>
       <c r="H12" s="19">
-        <v>4.5628785251699999E-2</v>
+        <v>4.9265227286000003E-2</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>13</v>
@@ -1439,25 +1429,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F13" s="17">
-        <v>1209560</v>
+        <v>120661</v>
       </c>
       <c r="G13" s="18">
-        <v>15302.14</v>
+        <v>14864.23</v>
       </c>
       <c r="H13" s="19">
-        <v>4.54421125904E-2</v>
+        <v>4.0765059535899997E-2</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>13</v>
@@ -1468,25 +1458,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" s="17">
-        <v>781265</v>
+        <v>949896</v>
       </c>
       <c r="G14" s="18">
-        <v>14686.22</v>
+        <v>14844.02</v>
       </c>
       <c r="H14" s="19">
-        <v>4.36130412326E-2</v>
+        <v>4.0709633734899997E-2</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>13</v>
@@ -1497,25 +1487,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" s="17">
-        <v>3148237</v>
+        <v>769799</v>
       </c>
       <c r="G15" s="18">
-        <v>14088.36</v>
+        <v>14289.01</v>
       </c>
       <c r="H15" s="19">
-        <v>4.1837601886599997E-2</v>
+        <v>3.9187522216599997E-2</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>13</v>
@@ -1526,25 +1516,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F16" s="17">
-        <v>806828</v>
+        <v>829024</v>
       </c>
       <c r="G16" s="18">
-        <v>13121.44</v>
+        <v>13907.71</v>
       </c>
       <c r="H16" s="19">
-        <v>3.8966180797400003E-2</v>
+        <v>3.8141809307099997E-2</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>13</v>
@@ -1555,25 +1545,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F17" s="17">
-        <v>92747</v>
+        <v>111310</v>
       </c>
       <c r="G17" s="18">
-        <v>10654.27</v>
+        <v>12477.85</v>
       </c>
       <c r="H17" s="19">
-        <v>3.1639531262200003E-2</v>
+        <v>3.4220427033800002E-2</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>13</v>
@@ -1584,25 +1574,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F18" s="17">
-        <v>414443</v>
+        <v>1033158</v>
       </c>
       <c r="G18" s="18">
-        <v>10231.77</v>
+        <v>12317.31</v>
       </c>
       <c r="H18" s="19">
-        <v>3.03848510299E-2</v>
+        <v>3.37801470693E-2</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>13</v>
@@ -1613,25 +1603,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F19" s="17">
-        <v>273154</v>
+        <v>322184</v>
       </c>
       <c r="G19" s="18">
-        <v>9744.5</v>
+        <v>11840.58</v>
       </c>
       <c r="H19" s="19">
-        <v>2.8937826090799999E-2</v>
+        <v>3.2472717970499998E-2</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>13</v>
@@ -1642,25 +1632,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F20" s="17">
-        <v>3165496</v>
+        <v>1257439</v>
       </c>
       <c r="G20" s="18">
-        <v>9548.7199999999993</v>
+        <v>10214.18</v>
       </c>
       <c r="H20" s="19">
-        <v>2.8356426573900001E-2</v>
+        <v>2.8012325953599999E-2</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>13</v>
@@ -1671,25 +1661,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F21" s="17">
-        <v>509572</v>
+        <v>2944734</v>
       </c>
       <c r="G21" s="18">
-        <v>8886.68</v>
+        <v>9832.4699999999993</v>
       </c>
       <c r="H21" s="19">
-        <v>2.6390394618899998E-2</v>
+        <v>2.69654886216E-2</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>13</v>
@@ -1700,25 +1690,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F22" s="17">
-        <v>2607492</v>
+        <v>199651</v>
       </c>
       <c r="G22" s="18">
-        <v>8448.27</v>
+        <v>8603.56</v>
       </c>
       <c r="H22" s="19">
-        <v>2.50884671382E-2</v>
+        <v>2.3595210489900001E-2</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>13</v>
@@ -1729,25 +1719,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F23" s="17">
-        <v>1272840</v>
+        <v>2962990</v>
       </c>
       <c r="G23" s="18">
-        <v>8121.36</v>
+        <v>8585.26</v>
       </c>
       <c r="H23" s="19">
-        <v>2.4117656452400001E-2</v>
+        <v>2.35450228522E-2</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>13</v>
@@ -1767,16 +1757,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F24" s="17">
-        <v>541996</v>
+        <v>556946</v>
       </c>
       <c r="G24" s="18">
-        <v>8018.29</v>
+        <v>8163.16</v>
       </c>
       <c r="H24" s="19">
-        <v>2.38115738689E-2</v>
+        <v>2.2387416193100002E-2</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>13</v>
@@ -1796,16 +1786,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F25" s="17">
-        <v>2169634</v>
+        <v>94825</v>
       </c>
       <c r="G25" s="18">
-        <v>6767.09</v>
+        <v>8161.59</v>
       </c>
       <c r="H25" s="19">
-        <v>2.0095938586900002E-2</v>
+        <v>2.2383110477799999E-2</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>13</v>
@@ -1825,16 +1815,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F26" s="17">
-        <v>540333</v>
+        <v>1030440</v>
       </c>
       <c r="G26" s="18">
-        <v>6577.74</v>
+        <v>8004.97</v>
       </c>
       <c r="H26" s="19">
-        <v>1.9533633966899999E-2</v>
+        <v>2.1953581089100001E-2</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>13</v>
@@ -1845,25 +1835,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F27" s="17">
-        <v>125717</v>
+        <v>602833</v>
       </c>
       <c r="G27" s="18">
-        <v>6530.12</v>
+        <v>7542.65</v>
       </c>
       <c r="H27" s="19">
-        <v>1.9392218883600001E-2</v>
+        <v>2.0685671326899999E-2</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>13</v>
@@ -1883,16 +1873,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F28" s="17">
-        <v>416778</v>
+        <v>366778</v>
       </c>
       <c r="G28" s="18">
-        <v>6183.32</v>
+        <v>6646.75</v>
       </c>
       <c r="H28" s="19">
-        <v>1.83623417131E-2</v>
+        <v>1.82286710761E-2</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>13</v>
@@ -1912,16 +1902,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F29" s="17">
-        <v>304484</v>
+        <v>124394</v>
       </c>
       <c r="G29" s="18">
-        <v>5253.72</v>
+        <v>6634.55</v>
       </c>
       <c r="H29" s="19">
-        <v>1.5601748236400001E-2</v>
+        <v>1.8195212650999999E-2</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>13</v>
@@ -1941,16 +1931,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F30" s="17">
-        <v>116954</v>
+        <v>289966</v>
       </c>
       <c r="G30" s="18">
-        <v>5074.8100000000004</v>
+        <v>6550.62</v>
       </c>
       <c r="H30" s="19">
-        <v>1.5070446839100001E-2</v>
+        <v>1.79650351412E-2</v>
       </c>
       <c r="I30" s="18" t="s">
         <v>13</v>
@@ -1961,25 +1951,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F31" s="17">
-        <v>39427</v>
+        <v>254391</v>
       </c>
       <c r="G31" s="18">
-        <v>4853.72</v>
+        <v>5973.86</v>
       </c>
       <c r="H31" s="19">
-        <v>1.44138852946E-2</v>
+        <v>1.6383274381400002E-2</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>13</v>
@@ -1990,25 +1980,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D32" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="F32" s="17">
-        <v>85036</v>
+        <v>304484</v>
       </c>
       <c r="G32" s="18">
-        <v>4362.05</v>
+        <v>4983.1899999999996</v>
       </c>
       <c r="H32" s="19">
-        <v>1.2953793863099999E-2</v>
+        <v>1.3666367987299999E-2</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>13</v>
@@ -2031,13 +2021,13 @@
         <v>79</v>
       </c>
       <c r="F33" s="17">
-        <v>162766</v>
+        <v>76600</v>
       </c>
       <c r="G33" s="18">
-        <v>3744.92</v>
+        <v>4322.92</v>
       </c>
       <c r="H33" s="19">
-        <v>1.11211292199E-2</v>
+        <v>1.18555815652E-2</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>13</v>
@@ -2057,16 +2047,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="F34" s="17">
-        <v>98302</v>
+        <v>1669634</v>
       </c>
       <c r="G34" s="18">
-        <v>3430.99</v>
+        <v>4168.58</v>
       </c>
       <c r="H34" s="19">
-        <v>1.01888646866E-2</v>
+        <v>1.14323050625E-2</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>13</v>
@@ -2086,16 +2076,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="F35" s="17">
-        <v>120000</v>
+        <v>196823</v>
       </c>
       <c r="G35" s="18">
-        <v>2775.84</v>
+        <v>3097.8</v>
       </c>
       <c r="H35" s="19">
-        <v>8.2432936707999994E-3</v>
+        <v>8.4956974851000001E-3</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>13</v>
@@ -2115,16 +2105,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F36" s="17">
-        <v>19575</v>
+        <v>50569</v>
       </c>
       <c r="G36" s="18">
-        <v>1731.96</v>
+        <v>2786.6</v>
       </c>
       <c r="H36" s="19">
-        <v>5.1433277515999997E-3</v>
+        <v>7.6422333953000002E-3</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>13</v>
@@ -2135,25 +2125,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>22</v>
-      </c>
       <c r="F37" s="17">
-        <v>96823</v>
+        <v>103161</v>
       </c>
       <c r="G37" s="18">
-        <v>1621.25</v>
+        <v>2471.94</v>
       </c>
       <c r="H37" s="19">
-        <v>4.8145569858999999E-3</v>
+        <v>6.7792802768E-3</v>
       </c>
       <c r="I37" s="18" t="s">
         <v>13</v>
@@ -2164,23 +2154,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="16"/>
+        <v>89</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>90</v>
+      </c>
       <c r="D38" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F38" s="17">
-        <v>-19400</v>
+        <v>63042</v>
       </c>
       <c r="G38" s="18">
-        <v>-15.94</v>
-      </c>
-      <c r="H38" s="20" t="s">
-        <v>89</v>
+        <v>2241.14</v>
+      </c>
+      <c r="H38" s="19">
+        <v>6.1463126934999997E-3</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>13</v>
@@ -2191,23 +2183,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="16"/>
+        <v>91</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>92</v>
+      </c>
       <c r="D39" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="F39" s="17">
-        <v>-33750</v>
+        <v>501431</v>
       </c>
       <c r="G39" s="18">
-        <v>-25.01</v>
+        <v>1200.43</v>
       </c>
       <c r="H39" s="19">
-        <v>-7.4271130399999996E-5</v>
+        <v>3.2921719065000001E-3</v>
       </c>
       <c r="I39" s="18" t="s">
         <v>13</v>
@@ -2226,7 +2220,7 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>13</v>
@@ -2241,10 +2235,10 @@
         <v>13</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I41" s="12" t="s">
         <v>13</v>
@@ -2263,7 +2257,7 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>13</v>
@@ -2278,10 +2272,10 @@
         <v>13</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I43" s="12" t="s">
         <v>13</v>
@@ -2315,10 +2309,10 @@
         <v>13</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I45" s="12" t="s">
         <v>13</v>
@@ -2337,7 +2331,7 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>13</v>
@@ -2352,10 +2346,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I47" s="12" t="s">
         <v>13</v>
@@ -2374,25 +2368,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>92</v>
-      </c>
       <c r="H49" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>13</v>
@@ -2411,7 +2405,7 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>13</v>
@@ -2426,10 +2420,10 @@
         <v>13</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>13</v>
@@ -2448,7 +2442,7 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>13</v>
@@ -2463,10 +2457,10 @@
         <v>13</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>13</v>
@@ -2485,7 +2479,7 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>13</v>
@@ -2500,10 +2494,10 @@
         <v>13</v>
       </c>
       <c r="G55" s="12">
-        <v>14440.19</v>
+        <v>9243.9500000000007</v>
       </c>
       <c r="H55" s="13">
-        <v>4.2882416433399996E-2</v>
+        <v>2.53514761339E-2</v>
       </c>
       <c r="I55" s="12" t="s">
         <v>13</v>
@@ -2522,7 +2516,7 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>13</v>
@@ -2537,10 +2531,10 @@
         <v>13</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I57" s="12" t="s">
         <v>13</v>
@@ -2559,7 +2553,7 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>13</v>
@@ -2574,10 +2568,10 @@
         <v>13</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>13</v>
@@ -2596,7 +2590,7 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>13</v>
@@ -2611,10 +2605,10 @@
         <v>13</v>
       </c>
       <c r="G61" s="12">
-        <v>14440.19</v>
+        <v>9243.9500000000007</v>
       </c>
       <c r="H61" s="13">
-        <v>4.2882416433399996E-2</v>
+        <v>2.53514761339E-2</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>13</v>
@@ -2625,28 +2619,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F62" s="17">
-        <v>10000000</v>
+        <v>3600000</v>
       </c>
       <c r="G62" s="18">
-        <v>9904.11</v>
+        <v>3578.04</v>
       </c>
       <c r="H62" s="19">
-        <v>2.9411813101099998E-2</v>
+        <v>9.8127527372999998E-3</v>
       </c>
       <c r="I62" s="18">
-        <v>6.43</v>
+        <v>5.6</v>
       </c>
       <c r="J62" s="14" t="s">
         <v>13</v>
@@ -2654,28 +2648,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F63" s="17">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="G63" s="18">
-        <v>2463.9499999999998</v>
+        <v>2985.28</v>
       </c>
       <c r="H63" s="19">
-        <v>7.3170872385E-3</v>
+        <v>8.1871120757999998E-3</v>
       </c>
       <c r="I63" s="18">
-        <v>6.51</v>
+        <v>5.62</v>
       </c>
       <c r="J63" s="14" t="s">
         <v>13</v>
@@ -2683,28 +2677,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="15" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F64" s="17">
-        <v>2000000</v>
+        <v>2700000</v>
       </c>
       <c r="G64" s="18">
-        <v>1973.57</v>
+        <v>2680.63</v>
       </c>
       <c r="H64" s="19">
-        <v>5.8608266649999999E-3</v>
+        <v>7.3516113208000004E-3</v>
       </c>
       <c r="I64" s="18">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J64" s="14" t="s">
         <v>13</v>
@@ -2712,35 +2706,35 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="F65" s="17">
-        <v>100000</v>
-      </c>
-      <c r="G65" s="18">
-        <v>98.56</v>
-      </c>
-      <c r="H65" s="19">
-        <v>2.9268942880000001E-4</v>
-      </c>
-      <c r="I65" s="18">
-        <v>6.51</v>
+        <v>13</v>
       </c>
       <c r="J65" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="12">
+        <v>4138.97</v>
+      </c>
+      <c r="H66" s="13">
+        <v>1.1351099819299999E-2</v>
+      </c>
+      <c r="I66" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J66" s="14" t="s">
@@ -2748,28 +2742,28 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="12">
-        <v>9085.35</v>
-      </c>
-      <c r="H67" s="13">
-        <v>2.6980376445499998E-2</v>
-      </c>
-      <c r="I67" s="12" t="s">
+      <c r="B67" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F67" s="17">
+        <v>1352870</v>
+      </c>
+      <c r="G67" s="18">
+        <v>4138.97</v>
+      </c>
+      <c r="H67" s="19">
+        <v>1.1351099819299999E-2</v>
+      </c>
+      <c r="I67" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J67" s="14" t="s">
@@ -2778,27 +2772,6 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="F68" s="17">
-        <v>3047445</v>
-      </c>
-      <c r="G68" s="18">
-        <v>9085.35</v>
-      </c>
-      <c r="H68" s="19">
-        <v>2.6980376445499998E-2</v>
-      </c>
-      <c r="I68" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J68" s="14" t="s">
@@ -2806,7 +2779,28 @@
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="I69" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J69" s="14" t="s">
@@ -2814,28 +2808,7 @@
       </c>
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="I70" s="12" t="s">
+      <c r="B70" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J70" s="14" t="s">
@@ -2843,7 +2816,28 @@
       </c>
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="12">
+        <v>33930.28</v>
+      </c>
+      <c r="H71" s="13">
+        <v>9.3053584630300001E-2</v>
+      </c>
+      <c r="I71" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J71" s="14" t="s">
@@ -2851,28 +2845,7 @@
       </c>
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="12">
-        <v>19534.84</v>
-      </c>
-      <c r="H72" s="13">
-        <v>5.8011781274699997E-2</v>
-      </c>
-      <c r="I72" s="12" t="s">
+      <c r="B72" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J72" s="14" t="s">
@@ -2880,7 +2853,28 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="12">
+        <v>1800</v>
+      </c>
+      <c r="H73" s="13">
+        <v>4.9364889512999999E-3</v>
+      </c>
+      <c r="I73" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J73" s="14" t="s">
@@ -2888,28 +2882,21 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="12">
-        <v>5000</v>
-      </c>
-      <c r="H74" s="13">
-        <v>1.48482867724E-2</v>
-      </c>
-      <c r="I74" s="12" t="s">
+      <c r="B74" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="16"/>
+      <c r="G74" s="18">
+        <v>1800</v>
+      </c>
+      <c r="H74" s="19">
+        <v>4.9364889512999999E-3</v>
+      </c>
+      <c r="I74" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J74" s="14" t="s">
@@ -2918,20 +2905,6 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="16"/>
-      <c r="G75" s="18">
-        <v>5000</v>
-      </c>
-      <c r="H75" s="19">
-        <v>1.48482867724E-2</v>
-      </c>
-      <c r="I75" s="18" t="s">
         <v>13</v>
       </c>
       <c r="J75" s="14" t="s">
@@ -2939,159 +2912,178 @@
       </c>
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="14" t="s">
+      <c r="B76" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="21">
+        <v>51.39740899001481</v>
+      </c>
+      <c r="H76" s="22">
+        <v>1.4095707866932996E-4</v>
+      </c>
+      <c r="I76" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="23" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C77" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="22">
-        <v>11.655916060029995</v>
-      </c>
-      <c r="H77" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="I77" s="22" t="s">
+      <c r="B77" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="21">
+        <v>364631.62740899</v>
+      </c>
+      <c r="H77" s="22">
+        <v>0.99999999999806921</v>
+      </c>
+      <c r="I77" s="21" t="s">
         <v>13</v>
       </c>
       <c r="J77" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C78" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="22">
-        <v>336739.18591606</v>
-      </c>
-      <c r="H78" s="24">
-        <v>0.99999999999815103</v>
-      </c>
-      <c r="I78" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="23" t="s">
+    <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C80" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H80" s="22" t="s">
-        <v>13</v>
+      <c r="B80" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G80" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="H80" s="21" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D81" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F81" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="G81" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="H81" s="22" t="s">
-        <v>9</v>
+      <c r="B81" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H82" s="11" t="s">
+      <c r="B82" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" s="17">
+        <v>385000</v>
+      </c>
+      <c r="G82" s="18">
+        <v>5602.91</v>
+      </c>
+      <c r="H82" s="19">
+        <v>1.53659462834E-2</v>
+      </c>
+      <c r="I82" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C83" s="16"/>
       <c r="D83" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F83" s="17">
-        <v>245000</v>
+        <v>575000</v>
       </c>
       <c r="G83" s="18">
-        <v>3080.75</v>
+        <v>5521.15</v>
       </c>
       <c r="H83" s="19">
-        <v>9.1487718947999997E-3</v>
+        <v>1.5141719985199999E-2</v>
       </c>
       <c r="I83" s="18" t="s">
         <v>13</v>
@@ -3100,116 +3092,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F84" s="17">
-        <v>140000</v>
-      </c>
-      <c r="G84" s="18">
-        <v>2442.65</v>
-      </c>
-      <c r="H84" s="19">
-        <v>7.2538335368999996E-3</v>
-      </c>
-      <c r="I84" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F85" s="17">
-        <v>-57000</v>
-      </c>
-      <c r="G85" s="18">
-        <v>-1318.3</v>
-      </c>
-      <c r="H85" s="19">
-        <v>-3.9148992904000004E-3</v>
-      </c>
-      <c r="I85" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F86" s="17">
-        <v>-1050000</v>
-      </c>
-      <c r="G86" s="18">
-        <v>-3287.03</v>
-      </c>
-      <c r="H86" s="19">
-        <v>-9.7613528139000004E-3</v>
-      </c>
-      <c r="I86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
     <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F87" s="17">
-        <v>-400000</v>
-      </c>
-      <c r="G87" s="18">
-        <v>-7552.4</v>
-      </c>
-      <c r="H87" s="19">
-        <v>-2.2428040204000001E-2</v>
-      </c>
-      <c r="I87" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="14" t="s">
-        <v>13</v>
-      </c>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C91" s="5"/>
@@ -3220,9 +3116,42 @@
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
     </row>
-    <row r="95" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+    </row>
+    <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+    </row>
+    <row r="95" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -3230,11 +3159,10 @@
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
-    </row>
-    <row r="96" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
@@ -3243,89 +3171,33 @@
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
     </row>
-    <row r="97" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B97" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
-    </row>
-    <row r="98" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-    </row>
-    <row r="99" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-    </row>
-    <row r="100" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="6" t="s">
+    <row r="99" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B99" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-    </row>
-    <row r="101" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="6" t="s">
+    </row>
+    <row r="114" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B114" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
-    </row>
-    <row r="104" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B104" s="25" t="s">
+    </row>
+    <row r="115" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="24" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="119" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B119" s="25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="25" t="s">
-        <v>135</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B87:I87"/>
     <mergeCell ref="B91:I91"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="B101:H101"/>
+    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="B95:H95"/>
     <mergeCell ref="B96:H96"/>
-    <mergeCell ref="B97:H97"/>
-    <mergeCell ref="B98:H98"/>
-    <mergeCell ref="B99:H99"/>
-    <mergeCell ref="B100:H100"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
